--- a/Dummy Patient Data for OCR Use Case.xlsx
+++ b/Dummy Patient Data for OCR Use Case.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HealthJournal\HealthJournalAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2D8CF1-6F70-4753-8A4A-D1392C1D51F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBBD6F9A-D8B1-4573-80F2-380928B5FC0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="976">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="975">
   <si>
     <t>Patient ID</t>
   </si>
@@ -886,9 +886,6 @@
     <t>Dialysis if necessary</t>
   </si>
   <si>
-    <t>01/13/2024</t>
-  </si>
-  <si>
     <t>Maintain renal function</t>
   </si>
   <si>
@@ -943,9 +940,6 @@
     <t>Adjust dose of medication</t>
   </si>
   <si>
-    <t>02/14/2024</t>
-  </si>
-  <si>
     <t>No symptoms of fatigue</t>
   </si>
   <si>
@@ -2948,6 +2942,9 @@
   </si>
   <si>
     <t>12345678901234</t>
+  </si>
+  <si>
+    <t>10/13/2025</t>
   </si>
 </sst>
 </file>
@@ -2955,7 +2952,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -3011,7 +3008,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -3321,9 +3318,24 @@
     <col min="5" max="5" width="29.88671875" customWidth="1"/>
     <col min="6" max="6" width="29.5546875" customWidth="1"/>
     <col min="8" max="8" width="26.5546875" customWidth="1"/>
+    <col min="9" max="9" width="25.77734375" customWidth="1"/>
     <col min="10" max="10" width="24.44140625" customWidth="1"/>
     <col min="11" max="11" width="19.6640625" customWidth="1"/>
     <col min="12" max="12" width="13.88671875" customWidth="1"/>
+    <col min="13" max="13" width="16.5546875" customWidth="1"/>
+    <col min="15" max="15" width="26.6640625" customWidth="1"/>
+    <col min="16" max="16" width="20" customWidth="1"/>
+    <col min="23" max="23" width="24.6640625" customWidth="1"/>
+    <col min="24" max="24" width="23.6640625" customWidth="1"/>
+    <col min="25" max="25" width="22.109375" customWidth="1"/>
+    <col min="26" max="26" width="17.88671875" customWidth="1"/>
+    <col min="27" max="27" width="18.6640625" customWidth="1"/>
+    <col min="28" max="28" width="23.77734375" customWidth="1"/>
+    <col min="29" max="29" width="19.44140625" customWidth="1"/>
+    <col min="30" max="30" width="14.77734375" customWidth="1"/>
+    <col min="31" max="31" width="20.33203125" customWidth="1"/>
+    <col min="32" max="32" width="17.6640625" customWidth="1"/>
+    <col min="33" max="33" width="16.5546875" customWidth="1"/>
     <col min="34" max="34" width="20.77734375" customWidth="1"/>
     <col min="35" max="35" width="12" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="21.5546875" customWidth="1"/>
@@ -3531,8 +3543,8 @@
       <c r="AC2" t="s">
         <v>56</v>
       </c>
-      <c r="AD2" s="2">
-        <v>45292</v>
+      <c r="AD2" t="s">
+        <v>974</v>
       </c>
       <c r="AE2" t="s">
         <v>57</v>
@@ -3544,7 +3556,7 @@
         <v>80</v>
       </c>
       <c r="AI2" s="3" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.3">
@@ -3635,8 +3647,8 @@
       <c r="AC3" t="s">
         <v>78</v>
       </c>
-      <c r="AD3" s="2">
-        <v>45324</v>
+      <c r="AD3" t="s">
+        <v>974</v>
       </c>
       <c r="AE3" t="s">
         <v>79</v>
@@ -3736,8 +3748,8 @@
       <c r="AC4" t="s">
         <v>97</v>
       </c>
-      <c r="AD4" s="2">
-        <v>45354</v>
+      <c r="AD4" t="s">
+        <v>974</v>
       </c>
       <c r="AE4" t="s">
         <v>98</v>
@@ -3834,8 +3846,8 @@
       <c r="AC5" t="s">
         <v>117</v>
       </c>
-      <c r="AD5" s="2">
-        <v>45386</v>
+      <c r="AD5" t="s">
+        <v>974</v>
       </c>
       <c r="AE5" t="s">
         <v>118</v>
@@ -3932,8 +3944,8 @@
       <c r="AC6" t="s">
         <v>136</v>
       </c>
-      <c r="AD6" s="2">
-        <v>45417</v>
+      <c r="AD6" t="s">
+        <v>974</v>
       </c>
       <c r="AE6" t="s">
         <v>137</v>
@@ -4033,8 +4045,8 @@
       <c r="AC7" t="s">
         <v>156</v>
       </c>
-      <c r="AD7" s="2">
-        <v>45449</v>
+      <c r="AD7" t="s">
+        <v>974</v>
       </c>
       <c r="AE7" t="s">
         <v>157</v>
@@ -4131,8 +4143,8 @@
       <c r="AC8" t="s">
         <v>175</v>
       </c>
-      <c r="AD8" s="2">
-        <v>45480</v>
+      <c r="AD8" t="s">
+        <v>974</v>
       </c>
       <c r="AE8" t="s">
         <v>176</v>
@@ -4229,8 +4241,8 @@
       <c r="AC9" t="s">
         <v>193</v>
       </c>
-      <c r="AD9" s="2">
-        <v>45512</v>
+      <c r="AD9" t="s">
+        <v>974</v>
       </c>
       <c r="AE9" t="s">
         <v>194</v>
@@ -4330,8 +4342,8 @@
       <c r="AC10" t="s">
         <v>211</v>
       </c>
-      <c r="AD10" s="2">
-        <v>45544</v>
+      <c r="AD10" t="s">
+        <v>974</v>
       </c>
       <c r="AE10" t="s">
         <v>212</v>
@@ -4428,8 +4440,8 @@
       <c r="AC11" t="s">
         <v>230</v>
       </c>
-      <c r="AD11" s="2">
-        <v>45575</v>
+      <c r="AD11" t="s">
+        <v>974</v>
       </c>
       <c r="AE11" t="s">
         <v>231</v>
@@ -4526,8 +4538,8 @@
       <c r="AC12" t="s">
         <v>247</v>
       </c>
-      <c r="AD12" s="2">
-        <v>45607</v>
+      <c r="AD12" t="s">
+        <v>974</v>
       </c>
       <c r="AE12" t="s">
         <v>248</v>
@@ -4627,8 +4639,8 @@
       <c r="AC13" t="s">
         <v>267</v>
       </c>
-      <c r="AD13" s="2">
-        <v>45638</v>
+      <c r="AD13" t="s">
+        <v>974</v>
       </c>
       <c r="AE13" t="s">
         <v>268</v>
@@ -4726,10 +4738,10 @@
         <v>287</v>
       </c>
       <c r="AD14" t="s">
+        <v>974</v>
+      </c>
+      <c r="AE14" t="s">
         <v>288</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>289</v>
       </c>
       <c r="AF14" t="s">
         <v>58</v>
@@ -4740,52 +4752,52 @@
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>289</v>
+      </c>
+      <c r="B15" t="s">
         <v>290</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>291</v>
-      </c>
-      <c r="C15" t="s">
-        <v>292</v>
       </c>
       <c r="D15" t="s">
         <v>61</v>
       </c>
       <c r="E15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F15">
         <v>1234567826</v>
       </c>
       <c r="G15" t="s">
+        <v>293</v>
+      </c>
+      <c r="H15" t="s">
         <v>294</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>295</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>296</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>297</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" t="s">
         <v>298</v>
       </c>
-      <c r="L15" t="s">
+      <c r="M15" t="s">
         <v>299</v>
       </c>
-      <c r="M15" t="s">
-        <v>300</v>
-      </c>
       <c r="N15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O15" t="s">
         <v>147</v>
       </c>
       <c r="Q15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="R15">
         <v>68</v>
@@ -4803,13 +4815,13 @@
         <v>1</v>
       </c>
       <c r="W15" t="s">
+        <v>301</v>
+      </c>
+      <c r="X15" t="s">
         <v>302</v>
       </c>
-      <c r="X15" t="s">
+      <c r="Y15" t="s">
         <v>303</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>304</v>
       </c>
       <c r="Z15" t="s">
         <v>153</v>
@@ -4818,16 +4830,16 @@
         <v>154</v>
       </c>
       <c r="AB15" t="s">
+        <v>304</v>
+      </c>
+      <c r="AC15" t="s">
         <v>305</v>
       </c>
-      <c r="AC15" t="s">
+      <c r="AD15" t="s">
+        <v>974</v>
+      </c>
+      <c r="AE15" t="s">
         <v>306</v>
-      </c>
-      <c r="AD15" t="s">
-        <v>307</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>308</v>
       </c>
       <c r="AF15" t="s">
         <v>99</v>
@@ -4838,52 +4850,52 @@
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>307</v>
+      </c>
+      <c r="B16" t="s">
+        <v>308</v>
+      </c>
+      <c r="C16" t="s">
         <v>309</v>
-      </c>
-      <c r="B16" t="s">
-        <v>310</v>
-      </c>
-      <c r="C16" t="s">
-        <v>311</v>
       </c>
       <c r="D16" t="s">
         <v>40</v>
       </c>
       <c r="E16" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F16">
         <v>1234567828</v>
       </c>
       <c r="G16" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H16" t="s">
         <v>104</v>
       </c>
       <c r="I16" t="s">
+        <v>312</v>
+      </c>
+      <c r="J16" t="s">
+        <v>313</v>
+      </c>
+      <c r="K16" t="s">
         <v>314</v>
       </c>
-      <c r="J16" t="s">
+      <c r="L16" t="s">
         <v>315</v>
       </c>
-      <c r="K16" t="s">
+      <c r="M16" t="s">
         <v>316</v>
       </c>
-      <c r="L16" t="s">
+      <c r="N16" t="s">
+        <v>313</v>
+      </c>
+      <c r="O16" t="s">
         <v>317</v>
       </c>
-      <c r="M16" t="s">
+      <c r="Q16" t="s">
         <v>318</v>
-      </c>
-      <c r="N16" t="s">
-        <v>315</v>
-      </c>
-      <c r="O16" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>320</v>
       </c>
       <c r="R16">
         <v>78</v>
@@ -4901,28 +4913,28 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="W16" t="s">
+        <v>319</v>
+      </c>
+      <c r="X16" t="s">
+        <v>320</v>
+      </c>
+      <c r="Y16" t="s">
         <v>321</v>
       </c>
-      <c r="X16" t="s">
+      <c r="Z16" t="s">
         <v>322</v>
       </c>
-      <c r="Y16" t="s">
+      <c r="AA16" t="s">
         <v>323</v>
       </c>
-      <c r="Z16" t="s">
+      <c r="AB16" t="s">
         <v>324</v>
       </c>
-      <c r="AA16" t="s">
+      <c r="AC16" t="s">
         <v>325</v>
       </c>
-      <c r="AB16" t="s">
+      <c r="AD16" t="s">
         <v>326</v>
-      </c>
-      <c r="AC16" t="s">
-        <v>327</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>328</v>
       </c>
       <c r="AE16" t="s">
         <v>58</v>
@@ -4933,52 +4945,52 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>327</v>
+      </c>
+      <c r="B17" t="s">
+        <v>328</v>
+      </c>
+      <c r="C17" t="s">
         <v>329</v>
-      </c>
-      <c r="B17" t="s">
-        <v>330</v>
-      </c>
-      <c r="C17" t="s">
-        <v>331</v>
       </c>
       <c r="D17" t="s">
         <v>61</v>
       </c>
       <c r="E17" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F17">
         <v>1234567830</v>
       </c>
       <c r="G17" t="s">
+        <v>331</v>
+      </c>
+      <c r="H17" t="s">
+        <v>332</v>
+      </c>
+      <c r="I17" t="s">
         <v>333</v>
       </c>
-      <c r="H17" t="s">
+      <c r="J17" t="s">
         <v>334</v>
       </c>
-      <c r="I17" t="s">
+      <c r="K17" t="s">
         <v>335</v>
       </c>
-      <c r="J17" t="s">
+      <c r="L17" t="s">
         <v>336</v>
       </c>
-      <c r="K17" t="s">
+      <c r="M17" t="s">
         <v>337</v>
       </c>
-      <c r="L17" t="s">
+      <c r="N17" t="s">
+        <v>334</v>
+      </c>
+      <c r="O17" t="s">
         <v>338</v>
       </c>
-      <c r="M17" t="s">
+      <c r="Q17" t="s">
         <v>339</v>
-      </c>
-      <c r="N17" t="s">
-        <v>336</v>
-      </c>
-      <c r="O17" t="s">
-        <v>340</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>341</v>
       </c>
       <c r="R17">
         <v>70</v>
@@ -4996,31 +5008,31 @@
         <v>1.2</v>
       </c>
       <c r="W17" t="s">
+        <v>340</v>
+      </c>
+      <c r="X17" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y17" t="s">
         <v>342</v>
       </c>
-      <c r="X17" t="s">
+      <c r="Z17" t="s">
         <v>343</v>
       </c>
-      <c r="Y17" t="s">
+      <c r="AA17" t="s">
         <v>344</v>
       </c>
-      <c r="Z17" t="s">
+      <c r="AB17" t="s">
         <v>345</v>
       </c>
-      <c r="AA17" t="s">
+      <c r="AC17" t="s">
         <v>346</v>
       </c>
-      <c r="AB17" t="s">
+      <c r="AD17" t="s">
         <v>347</v>
       </c>
-      <c r="AC17" t="s">
+      <c r="AE17" t="s">
         <v>348</v>
-      </c>
-      <c r="AD17" t="s">
-        <v>349</v>
-      </c>
-      <c r="AE17" t="s">
-        <v>350</v>
       </c>
       <c r="AF17" t="s">
         <v>119</v>
@@ -5031,49 +5043,49 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>349</v>
+      </c>
+      <c r="B18" t="s">
+        <v>350</v>
+      </c>
+      <c r="C18" t="s">
         <v>351</v>
-      </c>
-      <c r="B18" t="s">
-        <v>352</v>
-      </c>
-      <c r="C18" t="s">
-        <v>353</v>
       </c>
       <c r="D18" t="s">
         <v>40</v>
       </c>
       <c r="E18" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F18">
         <v>1234567832</v>
       </c>
       <c r="G18" t="s">
+        <v>353</v>
+      </c>
+      <c r="H18" t="s">
+        <v>354</v>
+      </c>
+      <c r="I18" t="s">
         <v>355</v>
       </c>
-      <c r="H18" t="s">
+      <c r="J18" t="s">
         <v>356</v>
       </c>
-      <c r="I18" t="s">
+      <c r="K18" t="s">
         <v>357</v>
       </c>
-      <c r="J18" t="s">
+      <c r="M18" t="s">
         <v>358</v>
       </c>
-      <c r="K18" t="s">
+      <c r="N18" t="s">
+        <v>356</v>
+      </c>
+      <c r="O18" t="s">
         <v>359</v>
       </c>
-      <c r="M18" t="s">
+      <c r="Q18" t="s">
         <v>360</v>
-      </c>
-      <c r="N18" t="s">
-        <v>358</v>
-      </c>
-      <c r="O18" t="s">
-        <v>361</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>362</v>
       </c>
       <c r="R18">
         <v>74</v>
@@ -5091,31 +5103,31 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="W18" t="s">
+        <v>361</v>
+      </c>
+      <c r="X18" t="s">
+        <v>362</v>
+      </c>
+      <c r="Y18" t="s">
         <v>363</v>
       </c>
-      <c r="X18" t="s">
+      <c r="Z18" t="s">
         <v>364</v>
       </c>
-      <c r="Y18" t="s">
+      <c r="AA18" t="s">
         <v>365</v>
       </c>
-      <c r="Z18" t="s">
+      <c r="AB18" t="s">
         <v>366</v>
       </c>
-      <c r="AA18" t="s">
+      <c r="AC18" t="s">
         <v>367</v>
       </c>
-      <c r="AB18" t="s">
+      <c r="AD18" t="s">
         <v>368</v>
       </c>
-      <c r="AC18" t="s">
+      <c r="AE18" t="s">
         <v>369</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>370</v>
-      </c>
-      <c r="AE18" t="s">
-        <v>371</v>
       </c>
       <c r="AF18" t="s">
         <v>58</v>
@@ -5126,52 +5138,52 @@
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>370</v>
+      </c>
+      <c r="B19" t="s">
+        <v>371</v>
+      </c>
+      <c r="C19" t="s">
         <v>372</v>
-      </c>
-      <c r="B19" t="s">
-        <v>373</v>
-      </c>
-      <c r="C19" t="s">
-        <v>374</v>
       </c>
       <c r="D19" t="s">
         <v>61</v>
       </c>
       <c r="E19" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F19">
         <v>1234567834</v>
       </c>
       <c r="G19" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H19" t="s">
         <v>124</v>
       </c>
       <c r="I19" t="s">
+        <v>375</v>
+      </c>
+      <c r="J19" t="s">
+        <v>376</v>
+      </c>
+      <c r="K19" t="s">
         <v>377</v>
       </c>
-      <c r="J19" t="s">
+      <c r="L19" t="s">
         <v>378</v>
       </c>
-      <c r="K19" t="s">
+      <c r="M19" t="s">
         <v>379</v>
       </c>
-      <c r="L19" t="s">
+      <c r="N19" t="s">
+        <v>376</v>
+      </c>
+      <c r="O19" t="s">
         <v>380</v>
       </c>
-      <c r="M19" t="s">
+      <c r="Q19" t="s">
         <v>381</v>
-      </c>
-      <c r="N19" t="s">
-        <v>378</v>
-      </c>
-      <c r="O19" t="s">
-        <v>382</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>383</v>
       </c>
       <c r="R19">
         <v>70</v>
@@ -5189,31 +5201,31 @@
         <v>1.2</v>
       </c>
       <c r="W19" t="s">
+        <v>382</v>
+      </c>
+      <c r="X19" t="s">
+        <v>383</v>
+      </c>
+      <c r="Y19" t="s">
         <v>384</v>
       </c>
-      <c r="X19" t="s">
+      <c r="Z19" t="s">
         <v>385</v>
       </c>
-      <c r="Y19" t="s">
+      <c r="AA19" t="s">
         <v>386</v>
       </c>
-      <c r="Z19" t="s">
+      <c r="AB19" t="s">
         <v>387</v>
       </c>
-      <c r="AA19" t="s">
+      <c r="AC19" t="s">
         <v>388</v>
       </c>
-      <c r="AB19" t="s">
+      <c r="AD19" t="s">
         <v>389</v>
       </c>
-      <c r="AC19" t="s">
+      <c r="AE19" t="s">
         <v>390</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>391</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>392</v>
       </c>
       <c r="AF19" t="s">
         <v>58</v>
@@ -5224,52 +5236,52 @@
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>391</v>
+      </c>
+      <c r="B20" t="s">
+        <v>392</v>
+      </c>
+      <c r="C20" t="s">
         <v>393</v>
-      </c>
-      <c r="B20" t="s">
-        <v>394</v>
-      </c>
-      <c r="C20" t="s">
-        <v>395</v>
       </c>
       <c r="D20" t="s">
         <v>61</v>
       </c>
       <c r="E20" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F20">
         <v>1234567836</v>
       </c>
       <c r="G20" t="s">
+        <v>395</v>
+      </c>
+      <c r="H20" t="s">
+        <v>396</v>
+      </c>
+      <c r="I20" t="s">
         <v>397</v>
       </c>
-      <c r="H20" t="s">
+      <c r="J20" t="s">
         <v>398</v>
       </c>
-      <c r="I20" t="s">
+      <c r="K20" t="s">
         <v>399</v>
       </c>
-      <c r="J20" t="s">
+      <c r="L20" t="s">
         <v>400</v>
       </c>
-      <c r="K20" t="s">
+      <c r="M20" t="s">
         <v>401</v>
       </c>
-      <c r="L20" t="s">
+      <c r="N20" t="s">
+        <v>398</v>
+      </c>
+      <c r="O20" t="s">
         <v>402</v>
       </c>
-      <c r="M20" t="s">
+      <c r="Q20" t="s">
         <v>403</v>
-      </c>
-      <c r="N20" t="s">
-        <v>400</v>
-      </c>
-      <c r="O20" t="s">
-        <v>404</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>405</v>
       </c>
       <c r="R20">
         <v>72</v>
@@ -5287,31 +5299,31 @@
         <v>0.9</v>
       </c>
       <c r="W20" t="s">
+        <v>404</v>
+      </c>
+      <c r="X20" t="s">
+        <v>405</v>
+      </c>
+      <c r="Y20" t="s">
         <v>406</v>
       </c>
-      <c r="X20" t="s">
+      <c r="Z20" t="s">
         <v>407</v>
       </c>
-      <c r="Y20" t="s">
+      <c r="AA20" t="s">
         <v>408</v>
       </c>
-      <c r="Z20" t="s">
+      <c r="AB20" t="s">
         <v>409</v>
       </c>
-      <c r="AA20" t="s">
+      <c r="AC20" t="s">
         <v>410</v>
       </c>
-      <c r="AB20" t="s">
+      <c r="AD20" t="s">
         <v>411</v>
       </c>
-      <c r="AC20" t="s">
+      <c r="AE20" t="s">
         <v>412</v>
-      </c>
-      <c r="AD20" t="s">
-        <v>413</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>414</v>
       </c>
       <c r="AF20" t="s">
         <v>99</v>
@@ -5322,46 +5334,46 @@
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>413</v>
+      </c>
+      <c r="B21" t="s">
+        <v>414</v>
+      </c>
+      <c r="C21" t="s">
         <v>415</v>
-      </c>
-      <c r="B21" t="s">
-        <v>416</v>
-      </c>
-      <c r="C21" t="s">
-        <v>417</v>
       </c>
       <c r="D21" t="s">
         <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F21">
         <v>1234567838</v>
       </c>
       <c r="G21" t="s">
+        <v>417</v>
+      </c>
+      <c r="H21" t="s">
+        <v>418</v>
+      </c>
+      <c r="I21" t="s">
         <v>419</v>
       </c>
-      <c r="H21" t="s">
+      <c r="J21" t="s">
         <v>420</v>
       </c>
-      <c r="I21" t="s">
+      <c r="K21" t="s">
         <v>421</v>
       </c>
-      <c r="J21" t="s">
+      <c r="M21" t="s">
         <v>422</v>
       </c>
-      <c r="K21" t="s">
+      <c r="N21" t="s">
+        <v>420</v>
+      </c>
+      <c r="O21" t="s">
         <v>423</v>
-      </c>
-      <c r="M21" t="s">
-        <v>424</v>
-      </c>
-      <c r="N21" t="s">
-        <v>422</v>
-      </c>
-      <c r="O21" t="s">
-        <v>425</v>
       </c>
       <c r="Q21" t="s">
         <v>49</v>
@@ -5382,31 +5394,31 @@
         <v>1.2</v>
       </c>
       <c r="W21" t="s">
+        <v>424</v>
+      </c>
+      <c r="X21" t="s">
+        <v>425</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>303</v>
+      </c>
+      <c r="Z21" t="s">
         <v>426</v>
       </c>
-      <c r="X21" t="s">
+      <c r="AA21" t="s">
         <v>427</v>
       </c>
-      <c r="Y21" t="s">
-        <v>304</v>
-      </c>
-      <c r="Z21" t="s">
+      <c r="AB21" t="s">
         <v>428</v>
       </c>
-      <c r="AA21" t="s">
+      <c r="AC21" t="s">
         <v>429</v>
       </c>
-      <c r="AB21" t="s">
+      <c r="AD21" t="s">
         <v>430</v>
       </c>
-      <c r="AC21" t="s">
+      <c r="AE21" t="s">
         <v>431</v>
-      </c>
-      <c r="AD21" t="s">
-        <v>432</v>
-      </c>
-      <c r="AE21" t="s">
-        <v>433</v>
       </c>
       <c r="AF21" t="s">
         <v>119</v>
@@ -5417,52 +5429,52 @@
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>432</v>
+      </c>
+      <c r="B22" t="s">
+        <v>433</v>
+      </c>
+      <c r="C22" t="s">
         <v>434</v>
-      </c>
-      <c r="B22" t="s">
-        <v>435</v>
-      </c>
-      <c r="C22" t="s">
-        <v>436</v>
       </c>
       <c r="D22" t="s">
         <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F22">
         <v>1234567840</v>
       </c>
       <c r="G22" t="s">
+        <v>436</v>
+      </c>
+      <c r="H22" t="s">
+        <v>437</v>
+      </c>
+      <c r="I22" t="s">
         <v>438</v>
       </c>
-      <c r="H22" t="s">
+      <c r="J22" t="s">
         <v>439</v>
       </c>
-      <c r="I22" t="s">
+      <c r="K22" t="s">
         <v>440</v>
-      </c>
-      <c r="J22" t="s">
-        <v>441</v>
-      </c>
-      <c r="K22" t="s">
-        <v>442</v>
       </c>
       <c r="L22" t="s">
         <v>220</v>
       </c>
       <c r="M22" t="s">
+        <v>441</v>
+      </c>
+      <c r="N22" t="s">
+        <v>439</v>
+      </c>
+      <c r="O22" t="s">
+        <v>442</v>
+      </c>
+      <c r="Q22" t="s">
         <v>443</v>
-      </c>
-      <c r="N22" t="s">
-        <v>441</v>
-      </c>
-      <c r="O22" t="s">
-        <v>444</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>445</v>
       </c>
       <c r="R22">
         <v>72</v>
@@ -5480,31 +5492,31 @@
         <v>1</v>
       </c>
       <c r="W22" t="s">
+        <v>444</v>
+      </c>
+      <c r="X22" t="s">
+        <v>445</v>
+      </c>
+      <c r="Y22" t="s">
         <v>446</v>
       </c>
-      <c r="X22" t="s">
+      <c r="Z22" t="s">
         <v>447</v>
       </c>
-      <c r="Y22" t="s">
+      <c r="AA22" t="s">
         <v>448</v>
       </c>
-      <c r="Z22" t="s">
+      <c r="AB22" t="s">
         <v>449</v>
       </c>
-      <c r="AA22" t="s">
+      <c r="AC22" t="s">
         <v>450</v>
       </c>
-      <c r="AB22" t="s">
+      <c r="AD22" t="s">
         <v>451</v>
       </c>
-      <c r="AC22" t="s">
+      <c r="AE22" t="s">
         <v>452</v>
-      </c>
-      <c r="AD22" t="s">
-        <v>453</v>
-      </c>
-      <c r="AE22" t="s">
-        <v>454</v>
       </c>
       <c r="AF22" t="s">
         <v>58</v>
@@ -5515,49 +5527,49 @@
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>453</v>
+      </c>
+      <c r="B23" t="s">
+        <v>454</v>
+      </c>
+      <c r="C23" t="s">
         <v>455</v>
-      </c>
-      <c r="B23" t="s">
-        <v>456</v>
-      </c>
-      <c r="C23" t="s">
-        <v>457</v>
       </c>
       <c r="D23" t="s">
         <v>61</v>
       </c>
       <c r="E23" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F23">
         <v>1234567842</v>
       </c>
       <c r="G23" t="s">
+        <v>457</v>
+      </c>
+      <c r="H23" t="s">
+        <v>458</v>
+      </c>
+      <c r="I23" t="s">
         <v>459</v>
       </c>
-      <c r="H23" t="s">
+      <c r="J23" t="s">
         <v>460</v>
       </c>
-      <c r="I23" t="s">
+      <c r="K23" t="s">
         <v>461</v>
       </c>
-      <c r="J23" t="s">
+      <c r="M23" t="s">
         <v>462</v>
       </c>
-      <c r="K23" t="s">
+      <c r="N23" t="s">
+        <v>460</v>
+      </c>
+      <c r="O23" t="s">
         <v>463</v>
       </c>
-      <c r="M23" t="s">
+      <c r="Q23" t="s">
         <v>464</v>
-      </c>
-      <c r="N23" t="s">
-        <v>462</v>
-      </c>
-      <c r="O23" t="s">
-        <v>465</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>466</v>
       </c>
       <c r="R23">
         <v>70</v>
@@ -5575,31 +5587,31 @@
         <v>1</v>
       </c>
       <c r="W23" t="s">
+        <v>465</v>
+      </c>
+      <c r="X23" t="s">
+        <v>466</v>
+      </c>
+      <c r="Y23" t="s">
         <v>467</v>
-      </c>
-      <c r="X23" t="s">
-        <v>468</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>469</v>
       </c>
       <c r="Z23" t="s">
         <v>172</v>
       </c>
       <c r="AA23" t="s">
+        <v>468</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>469</v>
+      </c>
+      <c r="AC23" t="s">
         <v>470</v>
       </c>
-      <c r="AB23" t="s">
+      <c r="AD23" t="s">
         <v>471</v>
       </c>
-      <c r="AC23" t="s">
+      <c r="AE23" t="s">
         <v>472</v>
-      </c>
-      <c r="AD23" t="s">
-        <v>473</v>
-      </c>
-      <c r="AE23" t="s">
-        <v>474</v>
       </c>
       <c r="AF23" t="s">
         <v>119</v>
@@ -5610,52 +5622,52 @@
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>473</v>
+      </c>
+      <c r="B24" t="s">
+        <v>474</v>
+      </c>
+      <c r="C24" t="s">
         <v>475</v>
-      </c>
-      <c r="B24" t="s">
-        <v>476</v>
-      </c>
-      <c r="C24" t="s">
-        <v>477</v>
       </c>
       <c r="D24" t="s">
         <v>40</v>
       </c>
       <c r="E24" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F24">
         <v>1234567844</v>
       </c>
       <c r="G24" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H24" t="s">
         <v>162</v>
       </c>
       <c r="I24" t="s">
+        <v>478</v>
+      </c>
+      <c r="J24" t="s">
+        <v>479</v>
+      </c>
+      <c r="K24" t="s">
         <v>480</v>
       </c>
-      <c r="J24" t="s">
+      <c r="L24" t="s">
+        <v>378</v>
+      </c>
+      <c r="M24" t="s">
         <v>481</v>
       </c>
-      <c r="K24" t="s">
+      <c r="N24" t="s">
+        <v>479</v>
+      </c>
+      <c r="O24" t="s">
         <v>482</v>
       </c>
-      <c r="L24" t="s">
-        <v>380</v>
-      </c>
-      <c r="M24" t="s">
+      <c r="Q24" t="s">
         <v>483</v>
-      </c>
-      <c r="N24" t="s">
-        <v>481</v>
-      </c>
-      <c r="O24" t="s">
-        <v>484</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>485</v>
       </c>
       <c r="R24">
         <v>72</v>
@@ -5673,31 +5685,31 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="W24" t="s">
+        <v>484</v>
+      </c>
+      <c r="X24" t="s">
+        <v>485</v>
+      </c>
+      <c r="Y24" t="s">
         <v>486</v>
       </c>
-      <c r="X24" t="s">
+      <c r="Z24" t="s">
         <v>487</v>
       </c>
-      <c r="Y24" t="s">
+      <c r="AA24" t="s">
         <v>488</v>
       </c>
-      <c r="Z24" t="s">
+      <c r="AB24" t="s">
         <v>489</v>
       </c>
-      <c r="AA24" t="s">
+      <c r="AC24" t="s">
         <v>490</v>
       </c>
-      <c r="AB24" t="s">
+      <c r="AD24" t="s">
         <v>491</v>
       </c>
-      <c r="AC24" t="s">
+      <c r="AE24" t="s">
         <v>492</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>493</v>
-      </c>
-      <c r="AE24" t="s">
-        <v>494</v>
       </c>
       <c r="AF24" t="s">
         <v>58</v>
@@ -5708,49 +5720,49 @@
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>493</v>
+      </c>
+      <c r="B25" t="s">
+        <v>494</v>
+      </c>
+      <c r="C25" t="s">
         <v>495</v>
-      </c>
-      <c r="B25" t="s">
-        <v>496</v>
-      </c>
-      <c r="C25" t="s">
-        <v>497</v>
       </c>
       <c r="D25" t="s">
         <v>61</v>
       </c>
       <c r="E25" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F25">
         <v>1234567846</v>
       </c>
       <c r="G25" t="s">
+        <v>497</v>
+      </c>
+      <c r="H25" t="s">
+        <v>498</v>
+      </c>
+      <c r="I25" t="s">
         <v>499</v>
       </c>
-      <c r="H25" t="s">
+      <c r="J25" t="s">
         <v>500</v>
       </c>
-      <c r="I25" t="s">
+      <c r="K25" t="s">
         <v>501</v>
       </c>
-      <c r="J25" t="s">
+      <c r="M25" t="s">
         <v>502</v>
       </c>
-      <c r="K25" t="s">
+      <c r="N25" t="s">
+        <v>500</v>
+      </c>
+      <c r="O25" t="s">
         <v>503</v>
       </c>
-      <c r="M25" t="s">
-        <v>504</v>
-      </c>
-      <c r="N25" t="s">
-        <v>502</v>
-      </c>
-      <c r="O25" t="s">
-        <v>505</v>
-      </c>
       <c r="Q25" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="R25">
         <v>74</v>
@@ -5768,31 +5780,31 @@
         <v>0.9</v>
       </c>
       <c r="W25" t="s">
+        <v>504</v>
+      </c>
+      <c r="X25" t="s">
+        <v>505</v>
+      </c>
+      <c r="Y25" t="s">
         <v>506</v>
       </c>
-      <c r="X25" t="s">
+      <c r="Z25" t="s">
         <v>507</v>
       </c>
-      <c r="Y25" t="s">
+      <c r="AA25" t="s">
         <v>508</v>
       </c>
-      <c r="Z25" t="s">
+      <c r="AB25" t="s">
         <v>509</v>
       </c>
-      <c r="AA25" t="s">
+      <c r="AC25" t="s">
         <v>510</v>
       </c>
-      <c r="AB25" t="s">
+      <c r="AD25" t="s">
         <v>511</v>
       </c>
-      <c r="AC25" t="s">
+      <c r="AE25" t="s">
         <v>512</v>
-      </c>
-      <c r="AD25" t="s">
-        <v>513</v>
-      </c>
-      <c r="AE25" t="s">
-        <v>514</v>
       </c>
       <c r="AF25" t="s">
         <v>99</v>
@@ -5803,49 +5815,49 @@
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>513</v>
+      </c>
+      <c r="B26" t="s">
+        <v>514</v>
+      </c>
+      <c r="C26" t="s">
         <v>515</v>
-      </c>
-      <c r="B26" t="s">
-        <v>516</v>
-      </c>
-      <c r="C26" t="s">
-        <v>517</v>
       </c>
       <c r="D26" t="s">
         <v>40</v>
       </c>
       <c r="E26" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F26">
         <v>1234567848</v>
       </c>
       <c r="G26" t="s">
+        <v>517</v>
+      </c>
+      <c r="H26" t="s">
+        <v>418</v>
+      </c>
+      <c r="I26" t="s">
+        <v>518</v>
+      </c>
+      <c r="J26" t="s">
         <v>519</v>
       </c>
-      <c r="H26" t="s">
-        <v>420</v>
-      </c>
-      <c r="I26" t="s">
+      <c r="K26" t="s">
         <v>520</v>
       </c>
-      <c r="J26" t="s">
+      <c r="M26" t="s">
         <v>521</v>
       </c>
-      <c r="K26" t="s">
+      <c r="N26" t="s">
+        <v>519</v>
+      </c>
+      <c r="O26" t="s">
         <v>522</v>
       </c>
-      <c r="M26" t="s">
+      <c r="Q26" t="s">
         <v>523</v>
-      </c>
-      <c r="N26" t="s">
-        <v>521</v>
-      </c>
-      <c r="O26" t="s">
-        <v>524</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>525</v>
       </c>
       <c r="R26">
         <v>70</v>
@@ -5863,31 +5875,31 @@
         <v>1.3</v>
       </c>
       <c r="W26" t="s">
+        <v>524</v>
+      </c>
+      <c r="X26" t="s">
+        <v>525</v>
+      </c>
+      <c r="Y26" t="s">
         <v>526</v>
       </c>
-      <c r="X26" t="s">
+      <c r="Z26" t="s">
         <v>527</v>
       </c>
-      <c r="Y26" t="s">
+      <c r="AA26" t="s">
         <v>528</v>
       </c>
-      <c r="Z26" t="s">
+      <c r="AB26" t="s">
         <v>529</v>
       </c>
-      <c r="AA26" t="s">
+      <c r="AC26" t="s">
         <v>530</v>
       </c>
-      <c r="AB26" t="s">
+      <c r="AD26" t="s">
         <v>531</v>
       </c>
-      <c r="AC26" t="s">
+      <c r="AE26" t="s">
         <v>532</v>
-      </c>
-      <c r="AD26" t="s">
-        <v>533</v>
-      </c>
-      <c r="AE26" t="s">
-        <v>534</v>
       </c>
       <c r="AF26" t="s">
         <v>119</v>
@@ -5898,49 +5910,49 @@
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>533</v>
+      </c>
+      <c r="B27" t="s">
+        <v>534</v>
+      </c>
+      <c r="C27" t="s">
         <v>535</v>
-      </c>
-      <c r="B27" t="s">
-        <v>536</v>
-      </c>
-      <c r="C27" t="s">
-        <v>537</v>
       </c>
       <c r="D27" t="s">
         <v>61</v>
       </c>
       <c r="E27" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F27">
         <v>1234567850</v>
       </c>
       <c r="G27" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="H27" t="s">
         <v>253</v>
       </c>
       <c r="I27" t="s">
+        <v>538</v>
+      </c>
+      <c r="J27" t="s">
+        <v>539</v>
+      </c>
+      <c r="K27" t="s">
         <v>540</v>
       </c>
-      <c r="J27" t="s">
+      <c r="M27" t="s">
         <v>541</v>
       </c>
-      <c r="K27" t="s">
+      <c r="N27" t="s">
+        <v>539</v>
+      </c>
+      <c r="O27" t="s">
         <v>542</v>
       </c>
-      <c r="M27" t="s">
-        <v>543</v>
-      </c>
-      <c r="N27" t="s">
-        <v>541</v>
-      </c>
-      <c r="O27" t="s">
-        <v>544</v>
-      </c>
       <c r="Q27" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="R27">
         <v>72</v>
@@ -5958,31 +5970,31 @@
         <v>1</v>
       </c>
       <c r="W27" t="s">
+        <v>543</v>
+      </c>
+      <c r="X27" t="s">
+        <v>544</v>
+      </c>
+      <c r="Y27" t="s">
         <v>545</v>
       </c>
-      <c r="X27" t="s">
+      <c r="Z27" t="s">
         <v>546</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>547</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>548</v>
       </c>
       <c r="AA27" t="s">
         <v>153</v>
       </c>
       <c r="AB27" t="s">
+        <v>547</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>548</v>
+      </c>
+      <c r="AD27" t="s">
         <v>549</v>
       </c>
-      <c r="AC27" t="s">
+      <c r="AE27" t="s">
         <v>550</v>
-      </c>
-      <c r="AD27" t="s">
-        <v>551</v>
-      </c>
-      <c r="AE27" t="s">
-        <v>552</v>
       </c>
       <c r="AF27" t="s">
         <v>58</v>
@@ -5993,46 +6005,46 @@
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>551</v>
+      </c>
+      <c r="B28" t="s">
+        <v>552</v>
+      </c>
+      <c r="C28" t="s">
         <v>553</v>
-      </c>
-      <c r="B28" t="s">
-        <v>554</v>
-      </c>
-      <c r="C28" t="s">
-        <v>555</v>
       </c>
       <c r="D28" t="s">
         <v>40</v>
       </c>
       <c r="E28" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F28">
         <v>1234567852</v>
       </c>
       <c r="G28" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="H28" t="s">
         <v>84</v>
       </c>
       <c r="I28" t="s">
+        <v>556</v>
+      </c>
+      <c r="J28" t="s">
+        <v>557</v>
+      </c>
+      <c r="K28" t="s">
         <v>558</v>
       </c>
-      <c r="J28" t="s">
+      <c r="M28" t="s">
         <v>559</v>
       </c>
-      <c r="K28" t="s">
+      <c r="N28" t="s">
+        <v>557</v>
+      </c>
+      <c r="O28" t="s">
         <v>560</v>
-      </c>
-      <c r="M28" t="s">
-        <v>561</v>
-      </c>
-      <c r="N28" t="s">
-        <v>559</v>
-      </c>
-      <c r="O28" t="s">
-        <v>562</v>
       </c>
       <c r="Q28" t="s">
         <v>204</v>
@@ -6053,31 +6065,31 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="W28" t="s">
+        <v>561</v>
+      </c>
+      <c r="X28" t="s">
+        <v>562</v>
+      </c>
+      <c r="Y28" t="s">
         <v>563</v>
       </c>
-      <c r="X28" t="s">
+      <c r="Z28" t="s">
         <v>564</v>
       </c>
-      <c r="Y28" t="s">
+      <c r="AA28" t="s">
         <v>565</v>
       </c>
-      <c r="Z28" t="s">
+      <c r="AB28" t="s">
         <v>566</v>
       </c>
-      <c r="AA28" t="s">
+      <c r="AC28" t="s">
         <v>567</v>
       </c>
-      <c r="AB28" t="s">
+      <c r="AD28" t="s">
         <v>568</v>
       </c>
-      <c r="AC28" t="s">
+      <c r="AE28" t="s">
         <v>569</v>
-      </c>
-      <c r="AD28" t="s">
-        <v>570</v>
-      </c>
-      <c r="AE28" t="s">
-        <v>571</v>
       </c>
       <c r="AF28" t="s">
         <v>99</v>
@@ -6088,49 +6100,49 @@
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>570</v>
+      </c>
+      <c r="B29" t="s">
+        <v>571</v>
+      </c>
+      <c r="C29" t="s">
         <v>572</v>
-      </c>
-      <c r="B29" t="s">
-        <v>573</v>
-      </c>
-      <c r="C29" t="s">
-        <v>574</v>
       </c>
       <c r="D29" t="s">
         <v>61</v>
       </c>
       <c r="E29" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F29">
         <v>1234567854</v>
       </c>
       <c r="G29" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H29" t="s">
         <v>274</v>
       </c>
       <c r="I29" t="s">
+        <v>575</v>
+      </c>
+      <c r="J29" t="s">
+        <v>576</v>
+      </c>
+      <c r="K29" t="s">
         <v>577</v>
       </c>
-      <c r="J29" t="s">
+      <c r="M29" t="s">
         <v>578</v>
       </c>
-      <c r="K29" t="s">
+      <c r="N29" t="s">
+        <v>576</v>
+      </c>
+      <c r="O29" t="s">
         <v>579</v>
       </c>
-      <c r="M29" t="s">
+      <c r="Q29" t="s">
         <v>580</v>
-      </c>
-      <c r="N29" t="s">
-        <v>578</v>
-      </c>
-      <c r="O29" t="s">
-        <v>581</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>582</v>
       </c>
       <c r="R29">
         <v>66</v>
@@ -6148,31 +6160,31 @@
         <v>0.9</v>
       </c>
       <c r="W29" t="s">
+        <v>581</v>
+      </c>
+      <c r="X29" t="s">
+        <v>582</v>
+      </c>
+      <c r="Y29" t="s">
         <v>583</v>
       </c>
-      <c r="X29" t="s">
+      <c r="Z29" t="s">
         <v>584</v>
       </c>
-      <c r="Y29" t="s">
+      <c r="AA29" t="s">
         <v>585</v>
       </c>
-      <c r="Z29" t="s">
+      <c r="AB29" t="s">
         <v>586</v>
       </c>
-      <c r="AA29" t="s">
+      <c r="AC29" t="s">
         <v>587</v>
       </c>
-      <c r="AB29" t="s">
+      <c r="AD29" t="s">
         <v>588</v>
       </c>
-      <c r="AC29" t="s">
+      <c r="AE29" t="s">
         <v>589</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>590</v>
-      </c>
-      <c r="AE29" t="s">
-        <v>591</v>
       </c>
       <c r="AF29" t="s">
         <v>58</v>
@@ -6183,49 +6195,49 @@
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>590</v>
+      </c>
+      <c r="B30" t="s">
+        <v>591</v>
+      </c>
+      <c r="C30" t="s">
         <v>592</v>
-      </c>
-      <c r="B30" t="s">
-        <v>593</v>
-      </c>
-      <c r="C30" t="s">
-        <v>594</v>
       </c>
       <c r="D30" t="s">
         <v>40</v>
       </c>
       <c r="E30" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F30">
         <v>1234567856</v>
       </c>
       <c r="G30" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="H30" t="s">
         <v>104</v>
       </c>
       <c r="I30" t="s">
+        <v>595</v>
+      </c>
+      <c r="J30" t="s">
+        <v>596</v>
+      </c>
+      <c r="K30" t="s">
         <v>597</v>
       </c>
-      <c r="J30" t="s">
+      <c r="M30" t="s">
         <v>598</v>
       </c>
-      <c r="K30" t="s">
+      <c r="N30" t="s">
+        <v>596</v>
+      </c>
+      <c r="O30" t="s">
         <v>599</v>
       </c>
-      <c r="M30" t="s">
-        <v>600</v>
-      </c>
-      <c r="N30" t="s">
-        <v>598</v>
-      </c>
-      <c r="O30" t="s">
-        <v>601</v>
-      </c>
       <c r="Q30" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="R30">
         <v>70</v>
@@ -6243,31 +6255,31 @@
         <v>1</v>
       </c>
       <c r="W30" t="s">
+        <v>600</v>
+      </c>
+      <c r="X30" t="s">
+        <v>601</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>506</v>
+      </c>
+      <c r="Z30" t="s">
         <v>602</v>
       </c>
-      <c r="X30" t="s">
+      <c r="AA30" t="s">
         <v>603</v>
       </c>
-      <c r="Y30" t="s">
-        <v>508</v>
-      </c>
-      <c r="Z30" t="s">
+      <c r="AB30" t="s">
         <v>604</v>
       </c>
-      <c r="AA30" t="s">
+      <c r="AC30" t="s">
         <v>605</v>
       </c>
-      <c r="AB30" t="s">
+      <c r="AD30" t="s">
         <v>606</v>
       </c>
-      <c r="AC30" t="s">
+      <c r="AE30" t="s">
         <v>607</v>
-      </c>
-      <c r="AD30" t="s">
-        <v>608</v>
-      </c>
-      <c r="AE30" t="s">
-        <v>609</v>
       </c>
       <c r="AF30" t="s">
         <v>119</v>
@@ -6278,52 +6290,52 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>608</v>
+      </c>
+      <c r="B31" t="s">
+        <v>609</v>
+      </c>
+      <c r="C31" t="s">
         <v>610</v>
-      </c>
-      <c r="B31" t="s">
-        <v>611</v>
-      </c>
-      <c r="C31" t="s">
-        <v>612</v>
       </c>
       <c r="D31" t="s">
         <v>61</v>
       </c>
       <c r="E31" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="F31">
         <v>1234567858</v>
       </c>
       <c r="G31" t="s">
+        <v>612</v>
+      </c>
+      <c r="H31" t="s">
+        <v>354</v>
+      </c>
+      <c r="I31" t="s">
+        <v>613</v>
+      </c>
+      <c r="J31" t="s">
         <v>614</v>
       </c>
-      <c r="H31" t="s">
-        <v>356</v>
-      </c>
-      <c r="I31" t="s">
+      <c r="K31" t="s">
         <v>615</v>
       </c>
-      <c r="J31" t="s">
+      <c r="L31" t="s">
         <v>616</v>
       </c>
-      <c r="K31" t="s">
+      <c r="M31" t="s">
+        <v>299</v>
+      </c>
+      <c r="N31" t="s">
+        <v>614</v>
+      </c>
+      <c r="O31" t="s">
         <v>617</v>
       </c>
-      <c r="L31" t="s">
+      <c r="Q31" t="s">
         <v>618</v>
-      </c>
-      <c r="M31" t="s">
-        <v>300</v>
-      </c>
-      <c r="N31" t="s">
-        <v>616</v>
-      </c>
-      <c r="O31" t="s">
-        <v>619</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>620</v>
       </c>
       <c r="R31">
         <v>68</v>
@@ -6341,31 +6353,31 @@
         <v>0.8</v>
       </c>
       <c r="W31" t="s">
+        <v>619</v>
+      </c>
+      <c r="X31" t="s">
+        <v>620</v>
+      </c>
+      <c r="Y31" t="s">
         <v>621</v>
       </c>
-      <c r="X31" t="s">
+      <c r="Z31" t="s">
         <v>622</v>
       </c>
-      <c r="Y31" t="s">
+      <c r="AA31" t="s">
         <v>623</v>
       </c>
-      <c r="Z31" t="s">
+      <c r="AB31" t="s">
         <v>624</v>
       </c>
-      <c r="AA31" t="s">
+      <c r="AC31" t="s">
         <v>625</v>
       </c>
-      <c r="AB31" t="s">
+      <c r="AD31" t="s">
         <v>626</v>
       </c>
-      <c r="AC31" t="s">
+      <c r="AE31" t="s">
         <v>627</v>
-      </c>
-      <c r="AD31" t="s">
-        <v>628</v>
-      </c>
-      <c r="AE31" t="s">
-        <v>629</v>
       </c>
       <c r="AF31" t="s">
         <v>58</v>
@@ -6376,46 +6388,46 @@
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>628</v>
+      </c>
+      <c r="B32" t="s">
+        <v>629</v>
+      </c>
+      <c r="C32" t="s">
         <v>630</v>
-      </c>
-      <c r="B32" t="s">
-        <v>631</v>
-      </c>
-      <c r="C32" t="s">
-        <v>632</v>
       </c>
       <c r="D32" t="s">
         <v>40</v>
       </c>
       <c r="E32" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="F32">
         <v>1234567860</v>
       </c>
       <c r="G32" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="H32" t="s">
         <v>124</v>
       </c>
       <c r="I32" t="s">
+        <v>633</v>
+      </c>
+      <c r="J32" t="s">
+        <v>634</v>
+      </c>
+      <c r="K32" t="s">
         <v>635</v>
       </c>
-      <c r="J32" t="s">
+      <c r="M32" t="s">
         <v>636</v>
       </c>
-      <c r="K32" t="s">
+      <c r="N32" t="s">
+        <v>634</v>
+      </c>
+      <c r="O32" t="s">
         <v>637</v>
-      </c>
-      <c r="M32" t="s">
-        <v>638</v>
-      </c>
-      <c r="N32" t="s">
-        <v>636</v>
-      </c>
-      <c r="O32" t="s">
-        <v>639</v>
       </c>
       <c r="Q32" t="s">
         <v>49</v>
@@ -6436,31 +6448,31 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="W32" t="s">
+        <v>638</v>
+      </c>
+      <c r="X32" t="s">
+        <v>639</v>
+      </c>
+      <c r="Y32" t="s">
         <v>640</v>
       </c>
-      <c r="X32" t="s">
+      <c r="Z32" t="s">
         <v>641</v>
       </c>
-      <c r="Y32" t="s">
+      <c r="AA32" t="s">
         <v>642</v>
       </c>
-      <c r="Z32" t="s">
+      <c r="AB32" t="s">
         <v>643</v>
       </c>
-      <c r="AA32" t="s">
+      <c r="AC32" t="s">
         <v>644</v>
       </c>
-      <c r="AB32" t="s">
+      <c r="AD32" t="s">
         <v>645</v>
       </c>
-      <c r="AC32" t="s">
+      <c r="AE32" t="s">
         <v>646</v>
-      </c>
-      <c r="AD32" t="s">
-        <v>647</v>
-      </c>
-      <c r="AE32" t="s">
-        <v>648</v>
       </c>
       <c r="AF32" t="s">
         <v>58</v>
@@ -6471,10 +6483,10 @@
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B33" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C33" s="2">
         <v>26306</v>
@@ -6483,37 +6495,37 @@
         <v>61</v>
       </c>
       <c r="E33" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="F33">
         <v>1234567862</v>
       </c>
       <c r="G33" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H33" t="s">
         <v>142</v>
       </c>
       <c r="I33" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="J33" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="K33" s="2">
         <v>43108</v>
       </c>
       <c r="M33" t="s">
+        <v>653</v>
+      </c>
+      <c r="N33" t="s">
+        <v>652</v>
+      </c>
+      <c r="O33" t="s">
+        <v>654</v>
+      </c>
+      <c r="Q33" t="s">
         <v>655</v>
-      </c>
-      <c r="N33" t="s">
-        <v>654</v>
-      </c>
-      <c r="O33" t="s">
-        <v>656</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>657</v>
       </c>
       <c r="R33">
         <v>70</v>
@@ -6531,31 +6543,31 @@
         <v>1.3</v>
       </c>
       <c r="W33" t="s">
+        <v>656</v>
+      </c>
+      <c r="X33" t="s">
+        <v>341</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>657</v>
+      </c>
+      <c r="Z33" t="s">
         <v>658</v>
-      </c>
-      <c r="X33" t="s">
-        <v>343</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>659</v>
-      </c>
-      <c r="Z33" t="s">
-        <v>660</v>
       </c>
       <c r="AA33" t="s">
         <v>153</v>
       </c>
       <c r="AB33" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="AC33" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="AD33" s="2">
         <v>45299</v>
       </c>
       <c r="AE33" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="AF33" t="s">
         <v>119</v>
@@ -6566,10 +6578,10 @@
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B34" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C34" s="2">
         <v>30356</v>
@@ -6578,37 +6590,37 @@
         <v>61</v>
       </c>
       <c r="E34" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F34">
         <v>1234567864</v>
       </c>
       <c r="G34" t="s">
+        <v>665</v>
+      </c>
+      <c r="H34" t="s">
+        <v>458</v>
+      </c>
+      <c r="I34" t="s">
+        <v>666</v>
+      </c>
+      <c r="J34" t="s">
         <v>667</v>
-      </c>
-      <c r="H34" t="s">
-        <v>460</v>
-      </c>
-      <c r="I34" t="s">
-        <v>668</v>
-      </c>
-      <c r="J34" t="s">
-        <v>669</v>
       </c>
       <c r="K34" s="2">
         <v>42409</v>
       </c>
       <c r="M34" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="N34" t="s">
+        <v>667</v>
+      </c>
+      <c r="O34" t="s">
         <v>669</v>
       </c>
-      <c r="O34" t="s">
-        <v>671</v>
-      </c>
       <c r="P34" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="Q34">
         <v>70</v>
@@ -6626,31 +6638,31 @@
         <v>1.2</v>
       </c>
       <c r="V34" t="s">
+        <v>670</v>
+      </c>
+      <c r="W34" t="s">
+        <v>671</v>
+      </c>
+      <c r="X34" t="s">
         <v>672</v>
       </c>
-      <c r="W34" t="s">
+      <c r="Y34" t="s">
         <v>673</v>
       </c>
-      <c r="X34" t="s">
+      <c r="Z34" t="s">
         <v>674</v>
       </c>
-      <c r="Y34" t="s">
+      <c r="AA34" t="s">
         <v>675</v>
       </c>
-      <c r="Z34" t="s">
+      <c r="AB34" t="s">
         <v>676</v>
-      </c>
-      <c r="AA34" t="s">
-        <v>677</v>
-      </c>
-      <c r="AB34" t="s">
-        <v>678</v>
       </c>
       <c r="AC34" s="2">
         <v>45331</v>
       </c>
       <c r="AD34" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="AE34" t="s">
         <v>58</v>
@@ -6661,10 +6673,10 @@
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B35" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C35" s="2">
         <v>32942</v>
@@ -6673,37 +6685,37 @@
         <v>40</v>
       </c>
       <c r="E35" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F35">
         <v>1234567866</v>
       </c>
       <c r="G35" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="H35" t="s">
         <v>43</v>
       </c>
       <c r="I35" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="J35" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="K35" s="2">
         <v>43900</v>
       </c>
       <c r="M35" t="s">
+        <v>684</v>
+      </c>
+      <c r="N35" t="s">
+        <v>683</v>
+      </c>
+      <c r="O35" t="s">
+        <v>685</v>
+      </c>
+      <c r="P35" t="s">
         <v>686</v>
-      </c>
-      <c r="N35" t="s">
-        <v>685</v>
-      </c>
-      <c r="O35" t="s">
-        <v>687</v>
-      </c>
-      <c r="P35" t="s">
-        <v>688</v>
       </c>
       <c r="Q35">
         <v>70</v>
@@ -6721,31 +6733,31 @@
         <v>1</v>
       </c>
       <c r="V35" t="s">
+        <v>687</v>
+      </c>
+      <c r="W35" t="s">
+        <v>688</v>
+      </c>
+      <c r="X35" t="s">
         <v>689</v>
       </c>
-      <c r="W35" t="s">
+      <c r="Y35" t="s">
         <v>690</v>
       </c>
-      <c r="X35" t="s">
+      <c r="Z35" t="s">
         <v>691</v>
       </c>
-      <c r="Y35" t="s">
+      <c r="AA35" t="s">
         <v>692</v>
       </c>
-      <c r="Z35" t="s">
+      <c r="AB35" t="s">
         <v>693</v>
-      </c>
-      <c r="AA35" t="s">
-        <v>694</v>
-      </c>
-      <c r="AB35" t="s">
-        <v>695</v>
       </c>
       <c r="AC35" s="2">
         <v>45361</v>
       </c>
       <c r="AD35" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="AE35" t="s">
         <v>119</v>
@@ -6756,10 +6768,10 @@
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B36" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C36" s="2">
         <v>28591</v>
@@ -6768,37 +6780,37 @@
         <v>61</v>
       </c>
       <c r="E36" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F36">
         <v>1234567868</v>
       </c>
       <c r="G36" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H36" t="s">
         <v>64</v>
       </c>
       <c r="I36" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="J36" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="K36" s="2">
         <v>43932</v>
       </c>
       <c r="M36" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="N36" t="s">
+        <v>700</v>
+      </c>
+      <c r="O36" t="s">
         <v>702</v>
       </c>
-      <c r="O36" t="s">
-        <v>704</v>
-      </c>
       <c r="Q36" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="R36">
         <v>80</v>
@@ -6816,31 +6828,31 @@
         <v>1.5</v>
       </c>
       <c r="W36" t="s">
+        <v>703</v>
+      </c>
+      <c r="X36" t="s">
+        <v>704</v>
+      </c>
+      <c r="Y36" t="s">
         <v>705</v>
       </c>
-      <c r="X36" t="s">
+      <c r="Z36" t="s">
         <v>706</v>
       </c>
-      <c r="Y36" t="s">
+      <c r="AA36" t="s">
         <v>707</v>
       </c>
-      <c r="Z36" t="s">
+      <c r="AB36" t="s">
         <v>708</v>
       </c>
-      <c r="AA36" t="s">
+      <c r="AC36" t="s">
         <v>709</v>
-      </c>
-      <c r="AB36" t="s">
-        <v>710</v>
-      </c>
-      <c r="AC36" t="s">
-        <v>711</v>
       </c>
       <c r="AD36" s="2">
         <v>45393</v>
       </c>
       <c r="AE36" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="AF36" t="s">
         <v>58</v>
@@ -6851,10 +6863,10 @@
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C37" s="2">
         <v>25335</v>
@@ -6863,37 +6875,37 @@
         <v>61</v>
       </c>
       <c r="E37" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="F37">
         <v>1234567870</v>
       </c>
       <c r="G37" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H37" t="s">
         <v>84</v>
       </c>
       <c r="I37" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="J37" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="K37" s="2">
         <v>42502</v>
       </c>
       <c r="M37" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="N37" t="s">
+        <v>716</v>
+      </c>
+      <c r="O37" t="s">
         <v>718</v>
       </c>
-      <c r="O37" t="s">
-        <v>720</v>
-      </c>
       <c r="Q37" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="R37">
         <v>70</v>
@@ -6911,31 +6923,31 @@
         <v>1</v>
       </c>
       <c r="W37" t="s">
+        <v>719</v>
+      </c>
+      <c r="X37" t="s">
+        <v>720</v>
+      </c>
+      <c r="Y37" t="s">
         <v>721</v>
       </c>
-      <c r="X37" t="s">
+      <c r="Z37" t="s">
         <v>722</v>
       </c>
-      <c r="Y37" t="s">
+      <c r="AA37" t="s">
         <v>723</v>
       </c>
-      <c r="Z37" t="s">
+      <c r="AB37" t="s">
         <v>724</v>
       </c>
-      <c r="AA37" t="s">
+      <c r="AC37" t="s">
         <v>725</v>
-      </c>
-      <c r="AB37" t="s">
-        <v>726</v>
-      </c>
-      <c r="AC37" t="s">
-        <v>727</v>
       </c>
       <c r="AD37" s="2">
         <v>45424</v>
       </c>
       <c r="AE37" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="AF37" t="s">
         <v>58</v>
@@ -6946,10 +6958,10 @@
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B38" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C38" s="2">
         <v>34851</v>
@@ -6958,37 +6970,37 @@
         <v>61</v>
       </c>
       <c r="E38" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="F38">
         <v>1234567872</v>
       </c>
       <c r="G38" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="H38" t="s">
         <v>274</v>
       </c>
       <c r="I38" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="J38" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="K38" s="2">
         <v>43252</v>
       </c>
       <c r="M38" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="N38" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="O38" t="s">
         <v>48</v>
       </c>
       <c r="Q38" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="R38">
         <v>70</v>
@@ -7006,31 +7018,31 @@
         <v>1</v>
       </c>
       <c r="W38" t="s">
+        <v>734</v>
+      </c>
+      <c r="X38" t="s">
+        <v>735</v>
+      </c>
+      <c r="Y38" t="s">
         <v>736</v>
       </c>
-      <c r="X38" t="s">
+      <c r="Z38" t="s">
         <v>737</v>
       </c>
-      <c r="Y38" t="s">
+      <c r="AA38" t="s">
         <v>738</v>
       </c>
-      <c r="Z38" t="s">
+      <c r="AB38" t="s">
         <v>739</v>
       </c>
-      <c r="AA38" t="s">
+      <c r="AC38" t="s">
         <v>740</v>
-      </c>
-      <c r="AB38" t="s">
-        <v>741</v>
-      </c>
-      <c r="AC38" t="s">
-        <v>742</v>
       </c>
       <c r="AD38" s="2">
         <v>45444</v>
       </c>
       <c r="AE38" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="AF38" t="s">
         <v>119</v>
@@ -7041,10 +7053,10 @@
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B39" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C39" s="2">
         <v>31595</v>
@@ -7053,22 +7065,22 @@
         <v>40</v>
       </c>
       <c r="E39" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F39">
         <v>1234567874</v>
       </c>
       <c r="G39" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="H39" t="s">
         <v>104</v>
       </c>
       <c r="I39" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="J39" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="K39" s="2">
         <v>41822</v>
@@ -7077,10 +7089,10 @@
         <v>127</v>
       </c>
       <c r="N39" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="O39" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="Q39" t="s">
         <v>129</v>
@@ -7101,31 +7113,31 @@
         <v>1.2</v>
       </c>
       <c r="W39" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="X39" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="Y39" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="Z39" t="s">
         <v>75</v>
       </c>
       <c r="AA39" t="s">
+        <v>751</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>752</v>
+      </c>
+      <c r="AC39" t="s">
         <v>753</v>
-      </c>
-      <c r="AB39" t="s">
-        <v>754</v>
-      </c>
-      <c r="AC39" t="s">
-        <v>755</v>
       </c>
       <c r="AD39" s="2">
         <v>45475</v>
       </c>
       <c r="AE39" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="AF39" t="s">
         <v>58</v>
@@ -7136,10 +7148,10 @@
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B40" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C40" s="2">
         <v>28340</v>
@@ -7148,37 +7160,37 @@
         <v>61</v>
       </c>
       <c r="E40" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="F40">
         <v>1234567876</v>
       </c>
       <c r="G40" t="s">
+        <v>758</v>
+      </c>
+      <c r="H40" t="s">
+        <v>332</v>
+      </c>
+      <c r="I40" t="s">
+        <v>759</v>
+      </c>
+      <c r="J40" t="s">
         <v>760</v>
-      </c>
-      <c r="H40" t="s">
-        <v>334</v>
-      </c>
-      <c r="I40" t="s">
-        <v>761</v>
-      </c>
-      <c r="J40" t="s">
-        <v>762</v>
       </c>
       <c r="K40" s="2">
         <v>42950</v>
       </c>
       <c r="M40" t="s">
+        <v>761</v>
+      </c>
+      <c r="N40" t="s">
+        <v>760</v>
+      </c>
+      <c r="O40" t="s">
+        <v>762</v>
+      </c>
+      <c r="Q40" t="s">
         <v>763</v>
-      </c>
-      <c r="N40" t="s">
-        <v>762</v>
-      </c>
-      <c r="O40" t="s">
-        <v>764</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>765</v>
       </c>
       <c r="R40">
         <v>70</v>
@@ -7196,31 +7208,31 @@
         <v>0.9</v>
       </c>
       <c r="W40" t="s">
+        <v>764</v>
+      </c>
+      <c r="X40" t="s">
+        <v>765</v>
+      </c>
+      <c r="Y40" t="s">
         <v>766</v>
       </c>
-      <c r="X40" t="s">
+      <c r="Z40" t="s">
         <v>767</v>
       </c>
-      <c r="Y40" t="s">
+      <c r="AA40" t="s">
         <v>768</v>
       </c>
-      <c r="Z40" t="s">
+      <c r="AB40" t="s">
         <v>769</v>
       </c>
-      <c r="AA40" t="s">
+      <c r="AC40" t="s">
         <v>770</v>
-      </c>
-      <c r="AB40" t="s">
-        <v>771</v>
-      </c>
-      <c r="AC40" t="s">
-        <v>772</v>
       </c>
       <c r="AD40" s="2">
         <v>45507</v>
       </c>
       <c r="AE40" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="AF40" t="s">
         <v>119</v>
@@ -7231,10 +7243,10 @@
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B41" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C41" s="2">
         <v>23989</v>
@@ -7243,40 +7255,40 @@
         <v>40</v>
       </c>
       <c r="E41" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="F41">
         <v>1234567878</v>
       </c>
       <c r="G41" t="s">
+        <v>775</v>
+      </c>
+      <c r="H41" t="s">
+        <v>354</v>
+      </c>
+      <c r="I41" t="s">
+        <v>776</v>
+      </c>
+      <c r="J41" t="s">
         <v>777</v>
-      </c>
-      <c r="H41" t="s">
-        <v>356</v>
-      </c>
-      <c r="I41" t="s">
-        <v>778</v>
-      </c>
-      <c r="J41" t="s">
-        <v>779</v>
       </c>
       <c r="K41" s="2">
         <v>42617</v>
       </c>
       <c r="L41" t="s">
+        <v>778</v>
+      </c>
+      <c r="M41" t="s">
+        <v>779</v>
+      </c>
+      <c r="N41" t="s">
+        <v>777</v>
+      </c>
+      <c r="O41" t="s">
         <v>780</v>
       </c>
-      <c r="M41" t="s">
+      <c r="Q41" t="s">
         <v>781</v>
-      </c>
-      <c r="N41" t="s">
-        <v>779</v>
-      </c>
-      <c r="O41" t="s">
-        <v>782</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>783</v>
       </c>
       <c r="R41">
         <v>76</v>
@@ -7294,31 +7306,31 @@
         <v>1.3</v>
       </c>
       <c r="W41" t="s">
+        <v>782</v>
+      </c>
+      <c r="X41" t="s">
+        <v>783</v>
+      </c>
+      <c r="Y41" t="s">
         <v>784</v>
       </c>
-      <c r="X41" t="s">
+      <c r="Z41" t="s">
+        <v>407</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>706</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>676</v>
+      </c>
+      <c r="AC41" t="s">
         <v>785</v>
-      </c>
-      <c r="Y41" t="s">
-        <v>786</v>
-      </c>
-      <c r="Z41" t="s">
-        <v>409</v>
-      </c>
-      <c r="AA41" t="s">
-        <v>708</v>
-      </c>
-      <c r="AB41" t="s">
-        <v>678</v>
-      </c>
-      <c r="AC41" t="s">
-        <v>787</v>
       </c>
       <c r="AD41" s="2">
         <v>45539</v>
       </c>
       <c r="AE41" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="AF41" t="s">
         <v>58</v>
@@ -7329,10 +7341,10 @@
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="B42" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C42" s="2">
         <v>29864</v>
@@ -7341,37 +7353,37 @@
         <v>61</v>
       </c>
       <c r="E42" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="F42">
         <v>1234567880</v>
       </c>
       <c r="G42" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="H42" t="s">
         <v>274</v>
       </c>
       <c r="I42" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="J42" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="K42" s="2">
         <v>43378</v>
       </c>
       <c r="M42" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="N42" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="O42" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="Q42" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="R42">
         <v>70</v>
@@ -7389,31 +7401,31 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="W42" t="s">
+        <v>793</v>
+      </c>
+      <c r="X42" t="s">
+        <v>794</v>
+      </c>
+      <c r="Y42" t="s">
         <v>795</v>
       </c>
-      <c r="X42" t="s">
+      <c r="Z42" t="s">
         <v>796</v>
       </c>
-      <c r="Y42" t="s">
+      <c r="AA42" t="s">
         <v>797</v>
       </c>
-      <c r="Z42" t="s">
+      <c r="AB42" t="s">
         <v>798</v>
       </c>
-      <c r="AA42" t="s">
+      <c r="AC42" t="s">
         <v>799</v>
-      </c>
-      <c r="AB42" t="s">
-        <v>800</v>
-      </c>
-      <c r="AC42" t="s">
-        <v>801</v>
       </c>
       <c r="AD42" s="2">
         <v>45570</v>
       </c>
       <c r="AE42" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="AF42" t="s">
         <v>58</v>
@@ -7424,10 +7436,10 @@
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B43" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C43" s="2">
         <v>32818</v>
@@ -7436,34 +7448,34 @@
         <v>40</v>
       </c>
       <c r="E43" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="F43">
         <v>1234567882</v>
       </c>
       <c r="G43" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="H43" t="s">
         <v>124</v>
       </c>
       <c r="I43" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="J43" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="K43" s="2">
         <v>42314</v>
       </c>
       <c r="M43" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="N43" t="s">
+        <v>806</v>
+      </c>
+      <c r="O43" t="s">
         <v>808</v>
-      </c>
-      <c r="O43" t="s">
-        <v>810</v>
       </c>
       <c r="Q43" t="s">
         <v>90</v>
@@ -7484,31 +7496,31 @@
         <v>1.3</v>
       </c>
       <c r="W43" t="s">
+        <v>809</v>
+      </c>
+      <c r="X43" t="s">
+        <v>810</v>
+      </c>
+      <c r="Y43" t="s">
         <v>811</v>
       </c>
-      <c r="X43" t="s">
+      <c r="Z43" t="s">
         <v>812</v>
       </c>
-      <c r="Y43" t="s">
+      <c r="AA43" t="s">
         <v>813</v>
       </c>
-      <c r="Z43" t="s">
+      <c r="AB43" t="s">
         <v>814</v>
       </c>
-      <c r="AA43" t="s">
+      <c r="AC43" t="s">
         <v>815</v>
-      </c>
-      <c r="AB43" t="s">
-        <v>816</v>
-      </c>
-      <c r="AC43" t="s">
-        <v>817</v>
       </c>
       <c r="AD43" s="2">
         <v>45602</v>
       </c>
       <c r="AE43" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="AF43" t="s">
         <v>58</v>
@@ -7519,10 +7531,10 @@
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B44" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C44" s="2">
         <v>26640</v>
@@ -7531,34 +7543,34 @@
         <v>61</v>
       </c>
       <c r="E44" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F44">
         <v>1234567884</v>
       </c>
       <c r="G44" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="H44" t="s">
         <v>253</v>
       </c>
       <c r="I44" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="J44" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="K44" s="2">
         <v>40519</v>
       </c>
       <c r="M44" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="N44" t="s">
+        <v>822</v>
+      </c>
+      <c r="O44" t="s">
         <v>824</v>
-      </c>
-      <c r="O44" t="s">
-        <v>826</v>
       </c>
       <c r="Q44" t="s">
         <v>129</v>
@@ -7579,16 +7591,16 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="W44" t="s">
+        <v>825</v>
+      </c>
+      <c r="X44" t="s">
+        <v>826</v>
+      </c>
+      <c r="Y44" t="s">
         <v>827</v>
       </c>
-      <c r="X44" t="s">
-        <v>828</v>
-      </c>
-      <c r="Y44" t="s">
-        <v>829</v>
-      </c>
       <c r="Z44" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AA44" t="s">
         <v>245</v>
@@ -7597,13 +7609,13 @@
         <v>246</v>
       </c>
       <c r="AC44" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="AD44" s="2">
         <v>45633</v>
       </c>
       <c r="AE44" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="AF44" t="s">
         <v>119</v>
@@ -7614,49 +7626,49 @@
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
+        <v>830</v>
+      </c>
+      <c r="B45" t="s">
+        <v>831</v>
+      </c>
+      <c r="C45" t="s">
         <v>832</v>
-      </c>
-      <c r="B45" t="s">
-        <v>833</v>
-      </c>
-      <c r="C45" t="s">
-        <v>834</v>
       </c>
       <c r="D45" t="s">
         <v>40</v>
       </c>
       <c r="E45" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="F45">
         <v>1234567886</v>
       </c>
       <c r="G45" t="s">
+        <v>834</v>
+      </c>
+      <c r="H45" t="s">
+        <v>418</v>
+      </c>
+      <c r="I45" t="s">
+        <v>835</v>
+      </c>
+      <c r="J45" t="s">
         <v>836</v>
       </c>
-      <c r="H45" t="s">
-        <v>420</v>
-      </c>
-      <c r="I45" t="s">
+      <c r="K45" t="s">
         <v>837</v>
       </c>
-      <c r="J45" t="s">
+      <c r="M45" t="s">
         <v>838</v>
       </c>
-      <c r="K45" t="s">
+      <c r="N45" t="s">
+        <v>836</v>
+      </c>
+      <c r="O45" t="s">
         <v>839</v>
       </c>
-      <c r="M45" t="s">
-        <v>840</v>
-      </c>
-      <c r="N45" t="s">
-        <v>838</v>
-      </c>
-      <c r="O45" t="s">
-        <v>841</v>
-      </c>
       <c r="Q45" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="R45">
         <v>73</v>
@@ -7674,31 +7686,31 @@
         <v>0.9</v>
       </c>
       <c r="W45" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="X45" t="s">
         <v>188</v>
       </c>
       <c r="Y45" t="s">
+        <v>841</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>842</v>
+      </c>
+      <c r="AA45" t="s">
         <v>843</v>
       </c>
-      <c r="Z45" t="s">
+      <c r="AB45" t="s">
         <v>844</v>
       </c>
-      <c r="AA45" t="s">
+      <c r="AC45" t="s">
         <v>845</v>
       </c>
-      <c r="AB45" t="s">
+      <c r="AD45" t="s">
         <v>846</v>
       </c>
-      <c r="AC45" t="s">
+      <c r="AE45" t="s">
         <v>847</v>
-      </c>
-      <c r="AD45" t="s">
-        <v>848</v>
-      </c>
-      <c r="AE45" t="s">
-        <v>849</v>
       </c>
       <c r="AF45" t="s">
         <v>58</v>
@@ -7709,49 +7721,49 @@
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
+        <v>848</v>
+      </c>
+      <c r="B46" t="s">
+        <v>849</v>
+      </c>
+      <c r="C46" t="s">
         <v>850</v>
-      </c>
-      <c r="B46" t="s">
-        <v>851</v>
-      </c>
-      <c r="C46" t="s">
-        <v>852</v>
       </c>
       <c r="D46" t="s">
         <v>61</v>
       </c>
       <c r="E46" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="F46">
         <v>1234567888</v>
       </c>
       <c r="G46" t="s">
+        <v>852</v>
+      </c>
+      <c r="H46" t="s">
+        <v>437</v>
+      </c>
+      <c r="I46" t="s">
+        <v>853</v>
+      </c>
+      <c r="J46" t="s">
         <v>854</v>
       </c>
-      <c r="H46" t="s">
-        <v>439</v>
-      </c>
-      <c r="I46" t="s">
+      <c r="K46" t="s">
         <v>855</v>
       </c>
-      <c r="J46" t="s">
+      <c r="M46" t="s">
         <v>856</v>
       </c>
-      <c r="K46" t="s">
+      <c r="N46" t="s">
+        <v>854</v>
+      </c>
+      <c r="O46" t="s">
         <v>857</v>
       </c>
-      <c r="M46" t="s">
-        <v>858</v>
-      </c>
-      <c r="N46" t="s">
-        <v>856</v>
-      </c>
-      <c r="O46" t="s">
-        <v>859</v>
-      </c>
       <c r="P46" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="Q46">
         <v>70</v>
@@ -7769,31 +7781,31 @@
         <v>0.8</v>
       </c>
       <c r="V46" t="s">
+        <v>858</v>
+      </c>
+      <c r="W46" t="s">
+        <v>302</v>
+      </c>
+      <c r="X46" t="s">
+        <v>859</v>
+      </c>
+      <c r="Y46" t="s">
         <v>860</v>
-      </c>
-      <c r="W46" t="s">
-        <v>303</v>
-      </c>
-      <c r="X46" t="s">
-        <v>861</v>
-      </c>
-      <c r="Y46" t="s">
-        <v>862</v>
       </c>
       <c r="Z46" t="s">
         <v>153</v>
       </c>
       <c r="AA46" t="s">
+        <v>861</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>862</v>
+      </c>
+      <c r="AC46" t="s">
         <v>863</v>
       </c>
-      <c r="AB46" t="s">
+      <c r="AD46" t="s">
         <v>864</v>
-      </c>
-      <c r="AC46" t="s">
-        <v>865</v>
-      </c>
-      <c r="AD46" t="s">
-        <v>866</v>
       </c>
       <c r="AE46" t="s">
         <v>58</v>
@@ -7804,49 +7816,49 @@
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
+        <v>865</v>
+      </c>
+      <c r="B47" t="s">
+        <v>866</v>
+      </c>
+      <c r="C47" t="s">
         <v>867</v>
-      </c>
-      <c r="B47" t="s">
-        <v>868</v>
-      </c>
-      <c r="C47" t="s">
-        <v>869</v>
       </c>
       <c r="D47" t="s">
         <v>40</v>
       </c>
       <c r="E47" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="F47">
         <v>1234567890</v>
       </c>
       <c r="G47" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="H47" t="s">
         <v>162</v>
       </c>
       <c r="I47" t="s">
+        <v>870</v>
+      </c>
+      <c r="J47" t="s">
+        <v>871</v>
+      </c>
+      <c r="K47" t="s">
         <v>872</v>
       </c>
-      <c r="J47" t="s">
+      <c r="M47" t="s">
         <v>873</v>
       </c>
-      <c r="K47" t="s">
+      <c r="N47" t="s">
+        <v>871</v>
+      </c>
+      <c r="O47" t="s">
         <v>874</v>
       </c>
-      <c r="M47" t="s">
-        <v>875</v>
-      </c>
-      <c r="N47" t="s">
-        <v>873</v>
-      </c>
-      <c r="O47" t="s">
-        <v>876</v>
-      </c>
       <c r="Q47" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="R47">
         <v>80</v>
@@ -7864,31 +7876,31 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="W47" t="s">
+        <v>875</v>
+      </c>
+      <c r="X47" t="s">
+        <v>876</v>
+      </c>
+      <c r="Y47" t="s">
         <v>877</v>
       </c>
-      <c r="X47" t="s">
+      <c r="Z47" t="s">
         <v>878</v>
       </c>
-      <c r="Y47" t="s">
+      <c r="AA47" t="s">
+        <v>706</v>
+      </c>
+      <c r="AB47" t="s">
         <v>879</v>
       </c>
-      <c r="Z47" t="s">
+      <c r="AC47" t="s">
         <v>880</v>
       </c>
-      <c r="AA47" t="s">
-        <v>708</v>
-      </c>
-      <c r="AB47" t="s">
+      <c r="AD47" t="s">
         <v>881</v>
       </c>
-      <c r="AC47" t="s">
+      <c r="AE47" t="s">
         <v>882</v>
-      </c>
-      <c r="AD47" t="s">
-        <v>883</v>
-      </c>
-      <c r="AE47" t="s">
-        <v>884</v>
       </c>
       <c r="AF47" t="s">
         <v>58</v>
@@ -7899,49 +7911,49 @@
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
+        <v>883</v>
+      </c>
+      <c r="B48" t="s">
+        <v>884</v>
+      </c>
+      <c r="C48" t="s">
         <v>885</v>
-      </c>
-      <c r="B48" t="s">
-        <v>886</v>
-      </c>
-      <c r="C48" t="s">
-        <v>887</v>
       </c>
       <c r="D48" t="s">
         <v>61</v>
       </c>
       <c r="E48" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="F48">
         <v>1234567892</v>
       </c>
       <c r="G48" t="s">
+        <v>887</v>
+      </c>
+      <c r="H48" t="s">
+        <v>498</v>
+      </c>
+      <c r="I48" t="s">
+        <v>888</v>
+      </c>
+      <c r="J48" t="s">
         <v>889</v>
       </c>
-      <c r="H48" t="s">
-        <v>500</v>
-      </c>
-      <c r="I48" t="s">
+      <c r="K48" t="s">
         <v>890</v>
       </c>
-      <c r="J48" t="s">
+      <c r="M48" t="s">
+        <v>462</v>
+      </c>
+      <c r="N48" t="s">
+        <v>889</v>
+      </c>
+      <c r="O48" t="s">
         <v>891</v>
       </c>
-      <c r="K48" t="s">
+      <c r="Q48" t="s">
         <v>892</v>
-      </c>
-      <c r="M48" t="s">
-        <v>464</v>
-      </c>
-      <c r="N48" t="s">
-        <v>891</v>
-      </c>
-      <c r="O48" t="s">
-        <v>893</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>894</v>
       </c>
       <c r="R48">
         <v>75</v>
@@ -7959,31 +7971,31 @@
         <v>1</v>
       </c>
       <c r="W48" t="s">
+        <v>893</v>
+      </c>
+      <c r="X48" t="s">
+        <v>894</v>
+      </c>
+      <c r="Y48" t="s">
         <v>895</v>
-      </c>
-      <c r="X48" t="s">
-        <v>896</v>
-      </c>
-      <c r="Y48" t="s">
-        <v>897</v>
       </c>
       <c r="Z48" t="s">
         <v>172</v>
       </c>
       <c r="AA48" t="s">
+        <v>896</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>897</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>676</v>
+      </c>
+      <c r="AD48" t="s">
         <v>898</v>
       </c>
-      <c r="AB48" t="s">
+      <c r="AE48" t="s">
         <v>899</v>
-      </c>
-      <c r="AC48" t="s">
-        <v>678</v>
-      </c>
-      <c r="AD48" t="s">
-        <v>900</v>
-      </c>
-      <c r="AE48" t="s">
-        <v>901</v>
       </c>
       <c r="AF48" t="s">
         <v>58</v>
@@ -7994,49 +8006,49 @@
     </row>
     <row r="49" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
+        <v>900</v>
+      </c>
+      <c r="B49" t="s">
+        <v>901</v>
+      </c>
+      <c r="C49" t="s">
         <v>902</v>
-      </c>
-      <c r="B49" t="s">
-        <v>903</v>
-      </c>
-      <c r="C49" t="s">
-        <v>904</v>
       </c>
       <c r="D49" t="s">
         <v>40</v>
       </c>
       <c r="E49" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="F49">
         <v>1234567894</v>
       </c>
       <c r="G49" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="H49" t="s">
         <v>181</v>
       </c>
       <c r="I49" t="s">
+        <v>905</v>
+      </c>
+      <c r="J49" t="s">
+        <v>906</v>
+      </c>
+      <c r="K49" t="s">
         <v>907</v>
       </c>
-      <c r="J49" t="s">
+      <c r="M49" t="s">
         <v>908</v>
       </c>
-      <c r="K49" t="s">
+      <c r="N49" t="s">
+        <v>906</v>
+      </c>
+      <c r="O49" t="s">
         <v>909</v>
       </c>
-      <c r="M49" t="s">
-        <v>910</v>
-      </c>
-      <c r="N49" t="s">
-        <v>908</v>
-      </c>
-      <c r="O49" t="s">
-        <v>911</v>
-      </c>
       <c r="Q49" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="R49">
         <v>68</v>
@@ -8054,31 +8066,31 @@
         <v>0.9</v>
       </c>
       <c r="W49" t="s">
+        <v>910</v>
+      </c>
+      <c r="X49" t="s">
+        <v>911</v>
+      </c>
+      <c r="Y49" t="s">
         <v>912</v>
       </c>
-      <c r="X49" t="s">
+      <c r="Z49" t="s">
         <v>913</v>
       </c>
-      <c r="Y49" t="s">
+      <c r="AA49" t="s">
+        <v>623</v>
+      </c>
+      <c r="AB49" t="s">
         <v>914</v>
       </c>
-      <c r="Z49" t="s">
+      <c r="AC49" t="s">
         <v>915</v>
       </c>
-      <c r="AA49" t="s">
-        <v>625</v>
-      </c>
-      <c r="AB49" t="s">
+      <c r="AD49" t="s">
         <v>916</v>
       </c>
-      <c r="AC49" t="s">
+      <c r="AE49" t="s">
         <v>917</v>
-      </c>
-      <c r="AD49" t="s">
-        <v>918</v>
-      </c>
-      <c r="AE49" t="s">
-        <v>919</v>
       </c>
       <c r="AF49" t="s">
         <v>58</v>
@@ -8089,49 +8101,49 @@
     </row>
     <row r="50" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
+        <v>918</v>
+      </c>
+      <c r="B50" t="s">
+        <v>919</v>
+      </c>
+      <c r="C50" t="s">
         <v>920</v>
-      </c>
-      <c r="B50" t="s">
-        <v>921</v>
-      </c>
-      <c r="C50" t="s">
-        <v>922</v>
       </c>
       <c r="D50" t="s">
         <v>61</v>
       </c>
       <c r="E50" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="F50">
         <v>1234567896</v>
       </c>
       <c r="G50" t="s">
+        <v>922</v>
+      </c>
+      <c r="H50" t="s">
+        <v>923</v>
+      </c>
+      <c r="I50" t="s">
         <v>924</v>
       </c>
-      <c r="H50" t="s">
+      <c r="J50" t="s">
         <v>925</v>
       </c>
-      <c r="I50" t="s">
+      <c r="K50" t="s">
         <v>926</v>
       </c>
-      <c r="J50" t="s">
+      <c r="M50" t="s">
         <v>927</v>
       </c>
-      <c r="K50" t="s">
+      <c r="N50" t="s">
+        <v>925</v>
+      </c>
+      <c r="O50" t="s">
         <v>928</v>
       </c>
-      <c r="M50" t="s">
+      <c r="Q50" t="s">
         <v>929</v>
-      </c>
-      <c r="N50" t="s">
-        <v>927</v>
-      </c>
-      <c r="O50" t="s">
-        <v>930</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>931</v>
       </c>
       <c r="R50">
         <v>75</v>
@@ -8149,31 +8161,31 @@
         <v>0.8</v>
       </c>
       <c r="W50" t="s">
+        <v>930</v>
+      </c>
+      <c r="X50" t="s">
+        <v>931</v>
+      </c>
+      <c r="Y50" t="s">
         <v>932</v>
-      </c>
-      <c r="X50" t="s">
-        <v>933</v>
-      </c>
-      <c r="Y50" t="s">
-        <v>934</v>
       </c>
       <c r="Z50" t="s">
         <v>190</v>
       </c>
       <c r="AA50" t="s">
+        <v>933</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>934</v>
+      </c>
+      <c r="AC50" t="s">
         <v>935</v>
       </c>
-      <c r="AB50" t="s">
+      <c r="AD50" t="s">
         <v>936</v>
       </c>
-      <c r="AC50" t="s">
+      <c r="AE50" t="s">
         <v>937</v>
-      </c>
-      <c r="AD50" t="s">
-        <v>938</v>
-      </c>
-      <c r="AE50" t="s">
-        <v>939</v>
       </c>
       <c r="AF50" t="s">
         <v>58</v>
@@ -8184,49 +8196,49 @@
     </row>
     <row r="51" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>938</v>
+      </c>
+      <c r="B51" t="s">
+        <v>939</v>
+      </c>
+      <c r="C51" t="s">
         <v>940</v>
-      </c>
-      <c r="B51" t="s">
-        <v>941</v>
-      </c>
-      <c r="C51" t="s">
-        <v>942</v>
       </c>
       <c r="D51" t="s">
         <v>40</v>
       </c>
       <c r="E51" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="F51">
         <v>1234567898</v>
       </c>
       <c r="G51" t="s">
+        <v>942</v>
+      </c>
+      <c r="H51" t="s">
+        <v>943</v>
+      </c>
+      <c r="I51" t="s">
         <v>944</v>
       </c>
-      <c r="H51" t="s">
+      <c r="J51" t="s">
         <v>945</v>
       </c>
-      <c r="I51" t="s">
+      <c r="K51" t="s">
         <v>946</v>
       </c>
-      <c r="J51" t="s">
+      <c r="M51" t="s">
         <v>947</v>
       </c>
-      <c r="K51" t="s">
-        <v>948</v>
-      </c>
-      <c r="M51" t="s">
-        <v>949</v>
-      </c>
       <c r="N51" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="O51" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="Q51" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="R51">
         <v>70</v>
@@ -8244,31 +8256,31 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="W51" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="X51" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="Y51" t="s">
         <v>171</v>
       </c>
       <c r="Z51" t="s">
+        <v>950</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>951</v>
+      </c>
+      <c r="AB51" t="s">
         <v>952</v>
       </c>
-      <c r="AA51" t="s">
+      <c r="AC51" t="s">
         <v>953</v>
       </c>
-      <c r="AB51" t="s">
+      <c r="AD51" t="s">
         <v>954</v>
       </c>
-      <c r="AC51" t="s">
+      <c r="AE51" t="s">
         <v>955</v>
-      </c>
-      <c r="AD51" t="s">
-        <v>956</v>
-      </c>
-      <c r="AE51" t="s">
-        <v>957</v>
       </c>
       <c r="AF51" t="s">
         <v>58</v>
@@ -8279,34 +8291,34 @@
     </row>
     <row r="52" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
+        <v>956</v>
+      </c>
+      <c r="B52" t="s">
+        <v>957</v>
+      </c>
+      <c r="C52" t="s">
         <v>958</v>
-      </c>
-      <c r="B52" t="s">
-        <v>959</v>
-      </c>
-      <c r="C52" t="s">
-        <v>960</v>
       </c>
       <c r="D52" t="s">
         <v>40</v>
       </c>
       <c r="E52" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="F52">
         <v>9876543210</v>
       </c>
       <c r="G52" t="s">
+        <v>960</v>
+      </c>
+      <c r="H52" t="s">
+        <v>961</v>
+      </c>
+      <c r="I52" t="s">
         <v>962</v>
       </c>
-      <c r="H52" t="s">
-        <v>963</v>
-      </c>
-      <c r="I52" t="s">
-        <v>964</v>
-      </c>
       <c r="M52" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="N52" t="s">
         <v>45</v>
@@ -8318,69 +8330,69 @@
         <v>70</v>
       </c>
       <c r="AH52" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="AI52">
         <v>12345678901234</v>
       </c>
       <c r="AJ52" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="AK52" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="53" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="B53" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C53" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="D53" t="s">
         <v>40</v>
       </c>
       <c r="E53" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="F53">
         <v>7337346748</v>
       </c>
       <c r="G53" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="H53" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="I53" t="s">
+        <v>853</v>
+      </c>
+      <c r="J53" t="s">
+        <v>854</v>
+      </c>
+      <c r="K53" t="s">
         <v>855</v>
-      </c>
-      <c r="J53" t="s">
-        <v>856</v>
-      </c>
-      <c r="K53" t="s">
-        <v>857</v>
       </c>
       <c r="L53" t="s">
         <v>67</v>
       </c>
       <c r="M53" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="N53" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="O53" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="P53" t="s">
         <v>89</v>
       </c>
       <c r="Q53" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="R53">
         <v>75</v>
@@ -8398,31 +8410,31 @@
         <v>0.8</v>
       </c>
       <c r="W53" t="s">
+        <v>930</v>
+      </c>
+      <c r="X53" t="s">
+        <v>931</v>
+      </c>
+      <c r="Y53" t="s">
         <v>932</v>
-      </c>
-      <c r="X53" t="s">
-        <v>933</v>
-      </c>
-      <c r="Y53" t="s">
-        <v>934</v>
       </c>
       <c r="Z53" t="s">
         <v>190</v>
       </c>
       <c r="AA53" t="s">
+        <v>933</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>934</v>
+      </c>
+      <c r="AC53" t="s">
         <v>935</v>
       </c>
-      <c r="AB53" t="s">
+      <c r="AD53" t="s">
         <v>936</v>
       </c>
-      <c r="AC53" t="s">
+      <c r="AE53" t="s">
         <v>937</v>
-      </c>
-      <c r="AD53" t="s">
-        <v>938</v>
-      </c>
-      <c r="AE53" t="s">
-        <v>939</v>
       </c>
       <c r="AF53" t="s">
         <v>58</v>
@@ -8431,16 +8443,16 @@
         <v>76</v>
       </c>
       <c r="AH53" t="s">
+        <v>969</v>
+      </c>
+      <c r="AJ53" t="s">
+        <v>970</v>
+      </c>
+      <c r="AK53" t="s">
+        <v>965</v>
+      </c>
+      <c r="AL53" t="s">
         <v>971</v>
-      </c>
-      <c r="AJ53" t="s">
-        <v>972</v>
-      </c>
-      <c r="AK53" t="s">
-        <v>967</v>
-      </c>
-      <c r="AL53" t="s">
-        <v>973</v>
       </c>
     </row>
   </sheetData>
